--- a/System Testing.xlsx
+++ b/System Testing.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Sheet2" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Sheet1" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="Sheet3" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="Sheet4" sheetId="4" r:id="rId8"/>
     <sheet state="visible" name="Sheet5" sheetId="5" r:id="rId9"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="120">
   <si>
     <t>Application Name</t>
   </si>
@@ -27,249 +27,180 @@
     <t>Module Name</t>
   </si>
   <si>
+    <t>REELS</t>
+  </si>
+  <si>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>Ujjwal Kumar</t>
+  </si>
+  <si>
+    <t>Scenario_ID</t>
+  </si>
+  <si>
+    <t>Scenario description</t>
+  </si>
+  <si>
+    <t>END TO END FLOW</t>
+  </si>
+  <si>
+    <t>INSTA_REELS_001</t>
+  </si>
+  <si>
+    <t>Reel Discovery &amp; Social Interaction / Sharing &amp; Curation Management</t>
+  </si>
+  <si>
+    <t>Open App -&gt; Navigate to Reels/Feed -&gt; Scroll to play -&gt; View full content -&gt; Double tap to Like -&gt; Post a Comment -&gt; Success; Open App -&gt; View Reel -&gt; Tap Share icon (Direct Message/Story) OR Tap three dots/Audio name to Save Reel/Audio -&gt; Success</t>
+  </si>
+  <si>
+    <t>INSTA_REELS_002</t>
+  </si>
+  <si>
+    <t>Core Creation &amp; Media Upload / Advanced Creative Tools &amp; Templates / Metadata &amp; Audience Tagging / Voiceover &amp; Audio Customization</t>
+  </si>
+  <si>
+    <t>Open App -&gt; Tap Create -&gt; Select Reel -&gt; Upload video from Gallery or record new clips -&gt; Search and Add Audio -&gt; Share -&gt; Success; Open App -&gt; Create Reel -&gt; Apply AR Filters/Effects OR use 'Template' from an existing Reel OR Remix an existing Reel -&gt; Record/Select clips -&gt; Share -&gt; Success; During Reel creation/editing -&gt; Tap 'Tag People' to search/select contacts -&gt; Tap 'Add Location' to search/select place -&gt; Share -&gt; Success; Open App -&gt; Create Reel -&gt; Record/Select video -&gt; Tap Music icon -&gt; Select Voiceover tool -&gt; Record audio overlay -&gt; Adjust levels -&gt; Share -&gt; Success</t>
+  </si>
+  <si>
+    <t>INSTA_REELS_003</t>
+  </si>
+  <si>
+    <t>Management &amp; Content Performance</t>
+  </si>
+  <si>
+    <t>Open own Reel on Profile -&gt; View Insights (Reach, Likes, etc.) OR Edit Captions OR Save progress to Drafts during creation -&gt; Success</t>
+  </si>
+  <si>
+    <t>INSTA_REELS_004</t>
+  </si>
+  <si>
+    <t>Security, Reporting &amp; Lifecycle</t>
+  </si>
+  <si>
+    <t>Open own Reel -&gt; Tap three dots -&gt; Delete Reel OR View other's Reel -&gt; Tap three dots -&gt; Report for inappropriate content -&gt; Submit -&gt; Success</t>
+  </si>
+  <si>
     <t>REGISTER</t>
   </si>
   <si>
-    <t>Author</t>
-  </si>
-  <si>
-    <t>Ujjwal Kumar</t>
-  </si>
-  <si>
-    <t>Scenario_ID</t>
-  </si>
-  <si>
-    <t>Scenario description</t>
-  </si>
-  <si>
-    <t>END TO END FLOW</t>
-  </si>
-  <si>
     <t>INSTA_RGSTR_001</t>
   </si>
   <si>
-    <t>Register with valid Email address</t>
-  </si>
-  <si>
-    <t>Open app -&gt; Sign up -&gt; Enter Email -&gt; Verify OTP -&gt; Set Password -&gt; Profile Info -&gt; Success</t>
+    <t>Register with valid Email address / Register with valid Phone Number / Register with already registered Email</t>
+  </si>
+  <si>
+    <t>Open app -&gt; Sign up -&gt; Enter Email -&gt; Verify OTP -&gt; Set Password -&gt; Profile Info -&gt; Success; Open app -&gt; Sign up -&gt; Enter Phone -&gt; Verify SMS OTP -&gt; Set Password -&gt; Profile Info -&gt; Success; Open app -&gt; Sign up -&gt; Enter existing Email -&gt; Receive "Account already exists" error</t>
   </si>
   <si>
     <t>INSTA_RGSTR_002</t>
   </si>
   <si>
-    <t>Register with valid Phone Number</t>
-  </si>
-  <si>
-    <t>Open app -&gt; Sign up -&gt; Enter Phone -&gt; Verify SMS OTP -&gt; Set Password -&gt; Profile Info -&gt; Success</t>
+    <t>Age restriction check (under 13 years old)</t>
+  </si>
+  <si>
+    <t>Open app -&gt; Sign up -&gt; Enter details -&gt; Select birth year 2020 -&gt; Receive eligibility error</t>
   </si>
   <si>
     <t>INSTA_RGSTR_003</t>
   </si>
   <si>
-    <t>Register with already registered Email</t>
-  </si>
-  <si>
-    <t>Open app -&gt; Sign up -&gt; Enter existing Email -&gt; Receive "Account already exists" error</t>
+    <t>OTP Verification failure (incorrect code)</t>
+  </si>
+  <si>
+    <t>Open app -&gt; Sign up -&gt; Enter Email -&gt; Receive OTP -&gt; Enter wrong code -&gt; Receive "Invalid OTP" error</t>
   </si>
   <si>
     <t>INSTA_RGSTR_004</t>
   </si>
   <si>
-    <t>Age restriction check (under 13 years old)</t>
-  </si>
-  <si>
-    <t>Open app -&gt; Sign up -&gt; Enter details -&gt; Select birth year 2020 -&gt; Receive eligibility error</t>
+    <t>Username availability check (taken username)</t>
+  </si>
+  <si>
+    <t>Open app -&gt; Sign up -&gt; Enter details -&gt; Enter "instagram" as username -&gt; Receive "Username not available" error</t>
   </si>
   <si>
     <t>INSTA_RGSTR_005</t>
   </si>
   <si>
-    <t>OTP Verification failure (incorrect code)</t>
-  </si>
-  <si>
-    <t>Open app -&gt; Sign up -&gt; Enter Email -&gt; Receive OTP -&gt; Enter wrong code -&gt; Receive "Invalid OTP" error</t>
+    <t>Registration via Facebook login</t>
+  </si>
+  <si>
+    <t>Open app -&gt; Sign up -&gt; Continue with Facebook -&gt; Authorize -&gt; Profile sync -&gt; Success</t>
   </si>
   <si>
     <t>INSTA_RGSTR_006</t>
   </si>
   <si>
-    <t>Username availability check (taken username)</t>
-  </si>
-  <si>
-    <t>Open app -&gt; Sign up -&gt; Enter details -&gt; Enter "instagram" as username -&gt; Receive "Username not available" error</t>
+    <t>Resend OTP when first OTP is not received</t>
+  </si>
+  <si>
+    <t>Open app -&gt; Sign up -&gt; Enter Email -&gt; Wait 60s -&gt; Tap Resend OTP -&gt; Receive new OTP -&gt; Verify -&gt; Success</t>
   </si>
   <si>
     <t>INSTA_RGSTR_007</t>
   </si>
   <si>
-    <t>Registration via Facebook login</t>
-  </si>
-  <si>
-    <t>Open app -&gt; Sign up -&gt; Continue with Facebook -&gt; Authorize -&gt; Profile sync -&gt; Success</t>
-  </si>
-  <si>
-    <t>INSTA_RGSTR_008</t>
-  </si>
-  <si>
-    <t>Resend OTP when first OTP is not received</t>
-  </si>
-  <si>
-    <t>Open app -&gt; Sign up -&gt; Enter Email -&gt; Wait 60s -&gt; Tap Resend OTP -&gt; Receive new OTP -&gt; Verify -&gt; Success</t>
-  </si>
-  <si>
-    <t>INSTA_RGSTR_009</t>
-  </si>
-  <si>
     <t>Register with already registered Phone Number</t>
   </si>
   <si>
     <t>Open app -&gt; Sign up -&gt; Enter existing Phone -&gt; Receive "Phone number already in use" error</t>
   </si>
   <si>
-    <t>REELS</t>
-  </si>
-  <si>
-    <t>INSTA_REELS_001</t>
-  </si>
-  <si>
-    <t>Reel Discovery &amp; Social Interaction</t>
-  </si>
-  <si>
-    <t>Open App -&gt; Navigate to Reels/Feed -&gt; Scroll to play -&gt; View full content -&gt; Double tap to Like -&gt; Post a Comment -&gt; Success</t>
-  </si>
-  <si>
-    <t>INSTA_REELS_002</t>
-  </si>
-  <si>
-    <t>Sharing &amp; Curation Management</t>
-  </si>
-  <si>
-    <t>Open App -&gt; View Reel -&gt; Tap Share icon (Direct Message/Story) OR Tap three dots/Audio name to Save Reel/Audio -&gt; Success</t>
-  </si>
-  <si>
-    <t>INSTA_REELS_003</t>
-  </si>
-  <si>
-    <t>Core Creation &amp; Media Upload</t>
-  </si>
-  <si>
-    <t>Open App -&gt; Tap Create -&gt; Select Reel -&gt; Upload video from Gallery or record new clips -&gt; Search and Add Audio -&gt; Share -&gt; Success</t>
-  </si>
-  <si>
-    <t>INSTA_REELS_004</t>
-  </si>
-  <si>
-    <t>Advanced Creative Tools &amp; Templates</t>
-  </si>
-  <si>
-    <t>Open App -&gt; Create Reel -&gt; Apply AR Filters/Effects OR use 'Template' from an existing Reel OR Remix an existing Reel -&gt; Record/Select clips -&gt; Share -&gt; Success</t>
-  </si>
-  <si>
-    <t>INSTA_REELS_005</t>
-  </si>
-  <si>
-    <t>Metadata &amp; Audience Tagging</t>
-  </si>
-  <si>
-    <t>During Reel creation/editing -&gt; Tap 'Tag People' to search/select contacts -&gt; Tap 'Add Location' to search/select place -&gt; Share -&gt; Success</t>
-  </si>
-  <si>
-    <t>INSTA_REELS_006</t>
-  </si>
-  <si>
-    <t>Voiceover &amp; Audio Customization</t>
-  </si>
-  <si>
-    <t>Open App -&gt; Create Reel -&gt; Record/Select video -&gt; Tap Music icon -&gt; Select Voiceover tool -&gt; Record audio overlay -&gt; Adjust levels -&gt; Share -&gt; Success</t>
-  </si>
-  <si>
-    <t>INSTA_REELS_007</t>
-  </si>
-  <si>
-    <t>Management &amp; Content Performance</t>
-  </si>
-  <si>
-    <t>Open own Reel on Profile -&gt; View Insights (Reach, Likes, etc.) OR Edit Captions OR Save progress to Drafts during creation -&gt; Success</t>
-  </si>
-  <si>
-    <t>INSTA_REELS_008</t>
-  </si>
-  <si>
-    <t>Security, Reporting &amp; Lifecycle</t>
-  </si>
-  <si>
-    <t>Open own Reel -&gt; Tap three dots -&gt; Delete Reel OR View other's Reel -&gt; Tap three dots -&gt; Report for inappropriate content -&gt; Submit -&gt; Success</t>
-  </si>
-  <si>
     <t>MESSAGES</t>
   </si>
   <si>
     <t>INSTA_MSG_001</t>
   </si>
   <si>
-    <t>Multimedia Messaging &amp; Location Sharing</t>
-  </si>
-  <si>
-    <t>Open App -&gt; Open DM -&gt; Select content (Text, Gallery Image, Voice Note, GIF, or Current Location) -&gt; Tap Send -&gt; Content appears correctly in chat -&gt; Success</t>
+    <t>Multimedia Messaging &amp; Location Sharing / Disappearing Media &amp; Feed Sharing / Message Interaction &amp; Management / Real-Time Video Communication</t>
+  </si>
+  <si>
+    <t>Open App -&gt; Open DM -&gt; Select content (Text</t>
+  </si>
+  <si>
+    <t>Gallery Image</t>
+  </si>
+  <si>
+    <t>Voice Note</t>
+  </si>
+  <si>
+    <t>GIF</t>
+  </si>
+  <si>
+    <t>or Current Location) -&gt; Tap Send -&gt; Content appears correctly in chat -&gt; Success; Open App -&gt; Open DM/Feed -&gt; Tap Camera (View Once) or Share icon on post -&gt; Select contact -&gt; Tap Send -&gt; Media/Post appears in DM as intended -&gt; Success; Open App -&gt; Open DM -&gt; Perform action on message (Long press to Reply/Forward/Unsend or Double tap to React) -&gt; Interaction reflects immediately -&gt; Success; Open App -&gt; Open DM -&gt; Tap Video Call icon -&gt; Wait for receiver to answer -&gt; Audio/Video stream established -&gt; Success</t>
   </si>
   <si>
     <t>INSTA_MSG_002</t>
   </si>
   <si>
-    <t>Disappearing Media &amp; Feed Sharing</t>
-  </si>
-  <si>
-    <t>Open App -&gt; Open DM/Feed -&gt; Tap Camera (View Once) or Share icon on post -&gt; Select contact -&gt; Tap Send -&gt; Media/Post appears in DM as intended -&gt; Success</t>
+    <t>Group Chat Creation &amp; Administration</t>
+  </si>
+  <si>
+    <t>Open App -&gt; Start New Group -&gt; Add multiple contacts -&gt; Name group -&gt; Manage members (Add/Remove) -&gt; Chat updates reflect for all members -&gt;Delete the group (if necessary)-&gt; Success</t>
   </si>
   <si>
     <t>INSTA_MSG_003</t>
   </si>
   <si>
-    <t>Message Interaction &amp; Management</t>
-  </si>
-  <si>
-    <t>Open App -&gt; Open DM -&gt; Perform action on message (Long press to Reply/Forward/Unsend or Double tap to React) -&gt; Interaction reflects immediately -&gt; Success</t>
+    <t>Inbox Organization &amp; List Management</t>
+  </si>
+  <si>
+    <t>Open App -&gt; Inbox -&gt; Perform action (Long press to Pin/Mark as Unread or Swipe to Delete) -&gt; Inbox list updates/sorts accordingly -&gt; Success</t>
   </si>
   <si>
     <t>INSTA_MSG_004</t>
   </si>
   <si>
-    <t>Real-Time Video Communication</t>
-  </si>
-  <si>
-    <t>Open App -&gt; Open DM -&gt; Tap Video Call icon -&gt; Wait for receiver to answer -&gt; Audio/Video stream established -&gt; Success</t>
+    <t>Chat Personalization &amp; Discovery</t>
+  </si>
+  <si>
+    <t>Open App -&gt; Open DM -&gt; Tap username -&gt; Select Theme/Background OR Tap 'Search in conversation' -&gt; Keyword/Theme applied or results found -&gt; Success</t>
   </si>
   <si>
     <t>INSTA_MSG_005</t>
   </si>
   <si>
-    <t>Group Chat Creation &amp; Administration</t>
-  </si>
-  <si>
-    <t>Open App -&gt; Start New Group -&gt; Add multiple contacts -&gt; Name group -&gt; Manage members (Add/Remove) -&gt; Chat updates reflect for all members -&gt;Delete the group (if necessary)-&gt; Success</t>
-  </si>
-  <si>
-    <t>INSTA_MSG_006</t>
-  </si>
-  <si>
-    <t>Inbox Organization &amp; List Management</t>
-  </si>
-  <si>
-    <t>Open App -&gt; Inbox -&gt; Perform action (Long press to Pin/Mark as Unread or Swipe to Delete) -&gt; Inbox list updates/sorts accordingly -&gt; Success</t>
-  </si>
-  <si>
-    <t>INSTA_MSG_007</t>
-  </si>
-  <si>
-    <t>Chat Personalization &amp; Discovery</t>
-  </si>
-  <si>
-    <t>Open App -&gt; Open DM -&gt; Tap username -&gt; Select Theme/Background OR Tap 'Search in conversation' -&gt; Keyword/Theme applied or results found -&gt; Success</t>
-  </si>
-  <si>
-    <t>INSTA_MSG_008</t>
-  </si>
-  <si>
     <t>User Privacy &amp; Safety Controls</t>
   </si>
   <si>
@@ -399,131 +330,59 @@
     <t>Access Direct Messages via Messenger icon or view likes/follows via the Heart (Activity) icon.</t>
   </si>
   <si>
-    <t>INSTA_HOME_006</t>
-  </si>
-  <si>
-    <t>Sponsored Ad Engagement</t>
-  </si>
-  <si>
-    <t>View sponsored content in feed -&gt; Click Call-to-Action (e.g., "Learn More") -&gt; External page opens.</t>
-  </si>
-  <si>
-    <t>INSTA_HOME_007</t>
-  </si>
-  <si>
-    <t>Feed &amp; Profile Controls</t>
-  </si>
-  <si>
-    <t>Filter feed to "Following" only -&gt; Toggle audio on videos -&gt; Visit user profiles directly from feed posts.</t>
-  </si>
-  <si>
-    <t>INSTA_HOME_008</t>
-  </si>
-  <si>
-    <t>Post Creation &amp; Catch Up</t>
-  </si>
-  <si>
-    <t>Use '+' shortcut to open camera/gallery for new posts -&gt; Scroll until "You're all caught up" message appears.</t>
-  </si>
-  <si>
-    <t>INSTA_HOME_009</t>
-  </si>
-  <si>
-    <t>Post Utilities &amp; Carousels</t>
-  </si>
-  <si>
-    <t>Report posts via menu -&gt; Copy direct post links -&gt; Swipe through multi-image carousel posts.</t>
-  </si>
-  <si>
-    <t>INSTA_HOME_010</t>
-  </si>
-  <si>
-    <t>App Search Access</t>
-  </si>
-  <si>
-    <t>Tap Search icon in bottom navigation to open the global search interface.</t>
-  </si>
-  <si>
     <t>PROFILE</t>
   </si>
   <si>
-    <t>INSTA_PROF_001</t>
-  </si>
-  <si>
-    <t>Profile Identity &amp; Metadata Management</t>
-  </si>
-  <si>
-    <t>Profile Screen -&gt; Edit Profile -&gt; Update Name, Username, Bio, Website, or Category -&gt; Save -&gt; Verify updates on profile -&gt; Success</t>
+    <t>NSTA_PROF_001</t>
+  </si>
+  <si>
+    <t>Profile Identity &amp; Metadata Management / Profile Picture Management</t>
+  </si>
+  <si>
+    <t>Profile Screen -&gt; Edit Profile -&gt; Update Name, Username, Bio, Website, or Category -&gt; Save -&gt; Verify updates on profile -&gt; Success; Profile Screen -&gt; Edit Profile -&gt; Tap Change Profile Photo -&gt; Select 'New profile picture' from gallery or 'Remove current photo' -&gt; Confirm -&gt; Success</t>
   </si>
   <si>
     <t>INSTA_PROF_002</t>
   </si>
   <si>
-    <t>Profile Picture Management</t>
-  </si>
-  <si>
-    <t>Profile Screen -&gt; Edit Profile -&gt; Tap Change Profile Photo -&gt; Select 'New profile picture' from gallery or 'Remove current photo' -&gt; Confirm -&gt; Success</t>
+    <t>Connection, Network &amp; Privacy Management</t>
+  </si>
+  <si>
+    <t>Profile Screen -&gt; Access Followers/Following/Close Friends list -&gt; Search/Scroll/Modify list OR Toggle 'Private Account' -&gt; Confirm -&gt; Success</t>
   </si>
   <si>
     <t>INSTA_PROF_003</t>
   </si>
   <si>
-    <t>Connection, Network &amp; Privacy Management</t>
-  </si>
-  <si>
-    <t>Profile Screen -&gt; Access Followers/Following/Close Friends list -&gt; Search/Scroll/Modify list OR Toggle 'Private Account' -&gt; Confirm -&gt; Success</t>
+    <t>Story Highlight Management</t>
+  </si>
+  <si>
+    <t>Profile Screen -&gt; Create 'New' highlight or long-press existing -&gt; Select archived stories, set cover/title, or delete highlight -&gt; Save/Confirm -&gt; Success</t>
   </si>
   <si>
     <t>INSTA_PROF_004</t>
   </si>
   <si>
-    <t>Story Highlight Management</t>
-  </si>
-  <si>
-    <t>Profile Screen -&gt; Create 'New' highlight or long-press existing -&gt; Select archived stories, set cover/title, or delete highlight -&gt; Save/Confirm -&gt; Success</t>
+    <t>Tabbed View Navigation</t>
+  </si>
+  <si>
+    <t>Profile Screen -&gt; Tap icons for Grid, Reels, Tagged, Saved, or Archive -&gt; Scroll through thumbnails and verify content loading -&gt; Success</t>
   </si>
   <si>
     <t>INSTA_PROF_005</t>
   </si>
   <si>
-    <t>Tabbed View Navigation</t>
-  </si>
-  <si>
-    <t>Profile Screen -&gt; Tap icons for Grid, Reels, Tagged, Saved, or Archive -&gt; Scroll through thumbnails and verify content loading -&gt; Success</t>
-  </si>
-  <si>
-    <t>INSTA_PROF_006</t>
-  </si>
-  <si>
-    <t>Settings &amp; Account Information Management</t>
-  </si>
-  <si>
-    <t>Profile Screen -&gt; Menu -&gt; Settings -&gt; Access 'Settings and privacy', 'Account Status', or 'Personal details' -&gt; Verify information -&gt; Success</t>
-  </si>
-  <si>
-    <t>INSTA_PROF_007</t>
-  </si>
-  <si>
-    <t>Discovery &amp; Sharing Tools</t>
-  </si>
-  <si>
-    <t>Profile Screen -&gt; Tap Menu or Discover People icon -&gt; Access QR code, share profile link, or browse suggestions -&gt; Success</t>
-  </si>
-  <si>
-    <t>INSTA_PROF_008</t>
-  </si>
-  <si>
-    <t>Account Lifecycle &amp; Session Control</t>
-  </si>
-  <si>
-    <t>Profile Screen -&gt; Menu/Edit Profile -&gt; Switch to Professional account OR Log out -&gt; Follow prompts/Confirm -&gt; Success</t>
+    <t>Settings &amp; Account Information Management / Discovery &amp; Sharing Tools / Account Lifecycle &amp; Session Control</t>
+  </si>
+  <si>
+    <t>Profile Screen -&gt; Menu -&gt; Settings -&gt; Access 'Settings and privacy', 'Account Status', or 'Personal details' -&gt; Verify information -&gt; Success; Profile Screen -&gt; Tap Menu or Discover People icon -&gt; Access QR code, share profile link, or browse suggestions -&gt; Success; Profile Screen -&gt; Menu/Edit Profile -&gt; Switch to Professional account OR Log out -&gt; Follow prompts/Confirm -&gt; Success</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -532,6 +391,11 @@
     </font>
     <font>
       <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -569,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -584,6 +448,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -823,9 +690,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="32.75"/>
-    <col customWidth="1" min="2" max="2" width="49.63"/>
-    <col customWidth="1" min="3" max="3" width="96.25"/>
+    <col customWidth="1" min="1" max="1" width="17.75"/>
+    <col customWidth="1" min="2" max="2" width="32.0"/>
+    <col customWidth="1" min="3" max="3" width="139.75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -875,7 +742,7 @@
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -886,7 +753,7 @@
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -916,59 +783,64 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -982,9 +854,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.75"/>
-    <col customWidth="1" min="2" max="2" width="33.0"/>
-    <col customWidth="1" min="3" max="3" width="131.38"/>
+    <col customWidth="1" min="1" max="1" width="32.75"/>
+    <col customWidth="1" min="2" max="2" width="49.63"/>
+    <col customWidth="1" min="3" max="3" width="96.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1001,7 +873,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2"/>
     </row>
@@ -1032,151 +904,80 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>41</v>
+        <v>25</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>44</v>
+        <v>28</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>47</v>
+        <v>31</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>53</v>
+        <v>37</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
+        <v>42</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -1209,7 +1010,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C2" s="2"/>
     </row>
@@ -1240,98 +1041,91 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
       <c r="D11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
       <c r="D12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
       <c r="D13" s="2"/>
     </row>
     <row r="14">
@@ -1342,7 +1136,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
+      <c r="B15" s="4"/>
       <c r="C15" s="1"/>
       <c r="D15" s="2"/>
     </row>
@@ -1360,7 +1154,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1"/>
-      <c r="B18" s="4"/>
+      <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="2"/>
     </row>
@@ -1384,19 +1178,19 @@
     </row>
     <row r="22">
       <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
+      <c r="B22" s="4"/>
       <c r="C22" s="1"/>
       <c r="D22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
+      <c r="B23" s="4"/>
       <c r="C23" s="1"/>
       <c r="D23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
+      <c r="B24" s="4"/>
       <c r="C24" s="1"/>
       <c r="D24" s="2"/>
     </row>
@@ -1408,27 +1202,9 @@
     </row>
     <row r="26">
       <c r="A26" s="1"/>
-      <c r="B26" s="4"/>
+      <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="2"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="2"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -1461,7 +1237,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="C2" s="2"/>
     </row>
@@ -1492,90 +1268,90 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14">
@@ -1689,7 +1465,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2"/>
     </row>
@@ -1720,113 +1496,83 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>129</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>132</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>135</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>141</v>
-      </c>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
     </row>
     <row r="16">
       <c r="A16" s="1"/>
@@ -1902,31 +1648,6 @@
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -1942,7 +1663,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="19.0"/>
     <col customWidth="1" min="2" max="2" width="50.75"/>
-    <col customWidth="1" min="3" max="3" width="127.25"/>
+    <col customWidth="1" min="3" max="3" width="269.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1959,7 +1680,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="C2" s="2"/>
     </row>
@@ -1990,91 +1711,73 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>145</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>157</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>160</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>163</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>166</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
     </row>
     <row r="14">
       <c r="A14" s="1"/>
